--- a/suivi_taches_16-04-2026.xlsx
+++ b/suivi_taches_16-04-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E43D00B-5B64-49F7-8E2E-F3EA9C2D5FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3972A92F-A5E7-4C93-A14C-7A2862F0A95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Suivi" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="272">
   <si>
     <t>Catégorie</t>
   </si>
@@ -86,9 +86,6 @@
     <t/>
   </si>
   <si>
-    <t>évacuation régulière en fonction de l'encombrement</t>
-  </si>
-  <si>
     <t>Colis Réception</t>
   </si>
   <si>
@@ -365,21 +362,12 @@
     <t>Régie William ajout WC + lavabo</t>
   </si>
   <si>
-    <t>Fin sol cuisine traiteur</t>
-  </si>
-  <si>
     <t>Fixations pour drapeaux parking</t>
   </si>
   <si>
     <t>Radiateur + TV local pose manager</t>
   </si>
   <si>
-    <t>Plans repérage extincteurs</t>
-  </si>
-  <si>
-    <t>Plans repérage blocs de secours</t>
-  </si>
-  <si>
     <t>Problème tringle chambre 205</t>
   </si>
   <si>
@@ -461,27 +449,18 @@
     <t>Laurent</t>
   </si>
   <si>
-    <t>HT doit aller chez cuisiniste</t>
-  </si>
-  <si>
     <t>BEGELEC</t>
   </si>
   <si>
     <t>Karim</t>
   </si>
   <si>
-    <t>Offre à corriger et compléter</t>
-  </si>
-  <si>
     <t>REXEL - ULTRASONS</t>
   </si>
   <si>
     <t>Paolo</t>
   </si>
   <si>
-    <t>Sterfput à créer et carrelage à acheter</t>
-  </si>
-  <si>
     <t>Adrien</t>
   </si>
   <si>
@@ -491,9 +470,6 @@
     <t>DORMA</t>
   </si>
   <si>
-    <t>teinte plus clair pour les couvres-murs demandées</t>
-  </si>
-  <si>
     <t>CHENE</t>
   </si>
   <si>
@@ -503,9 +479,6 @@
     <t>Marcia</t>
   </si>
   <si>
-    <t>test à faire - ICT doit configurer téléphones mardi 26/05</t>
-  </si>
-  <si>
     <t>Katia</t>
   </si>
   <si>
@@ -560,9 +533,6 @@
     <t>Promate démonté</t>
   </si>
   <si>
-    <t xml:space="preserve">Caméras reçues 27/05 - socles peints 28/05 - installation semaine 23 </t>
-  </si>
-  <si>
     <t>Jean-Marc</t>
   </si>
   <si>
@@ -572,18 +542,9 @@
     <t>Events</t>
   </si>
   <si>
-    <t>décision à prendre pour certaines choses à garder ou à jeter</t>
-  </si>
-  <si>
     <t>reste un morceau de goulotte à remplacer - pièce en commande</t>
   </si>
   <si>
-    <t>1 des 2 à été remplacé, l'autre à un problème de communication - fournisseur cherche une solution</t>
-  </si>
-  <si>
-    <t>offre de Stéphane DUBOIS envoyée à JM</t>
-  </si>
-  <si>
     <t>Céline</t>
   </si>
   <si>
@@ -593,9 +554,6 @@
     <t>A planifier</t>
   </si>
   <si>
-    <t>commandé chez SKIDATA mais responsable ne travaille plus là…</t>
-  </si>
-  <si>
     <t>Greg</t>
   </si>
   <si>
@@ -647,9 +605,6 @@
     <t>Renouvellement des moquettes</t>
   </si>
   <si>
-    <t>Fait le 12/05 - procédure ?</t>
-  </si>
-  <si>
     <t>chaque année</t>
   </si>
   <si>
@@ -674,18 +629,6 @@
     <t>reste radiateur - Adrien commande un IPTV - câble data à tirer</t>
   </si>
   <si>
-    <t>Marchandises commandées</t>
-  </si>
-  <si>
-    <t>Visite le 11/05 - devis en attente - dernier rappel le 22/05 - rappel par email + téléphone 05/06</t>
-  </si>
-  <si>
-    <t>Arrêté car hôtel full - reprend le 15/06</t>
-  </si>
-  <si>
-    <t>reste 29 chambres à peindre dont 23 avec tapisserie - Arrêté car hôtel full - reprend le 15/06</t>
-  </si>
-  <si>
     <t>Devis potence demandé chez ULTRASONS - rappel le 10/06</t>
   </si>
   <si>
@@ -693,9 +636,6 @@
   </si>
   <si>
     <t>Remplacement et stock ok</t>
-  </si>
-  <si>
-    <t>Rappel BEGELEC le 18/05 - attente des plans de Balto</t>
   </si>
   <si>
     <t>en suspens - Permis d'urbanisme nécessaire</t>
@@ -720,9 +660,6 @@
     <t>Etilux</t>
   </si>
   <si>
-    <t>validation Karim - attente réponse pour le sous-sol</t>
-  </si>
-  <si>
     <t>Engie, RenoEnergie, Interparking ?</t>
   </si>
   <si>
@@ -732,9 +669,6 @@
     <t>réparation faite</t>
   </si>
   <si>
-    <t xml:space="preserve">nouveau test </t>
-  </si>
-  <si>
     <t>méthode à déterminer</t>
   </si>
   <si>
@@ -748,80 +682,192 @@
   </si>
   <si>
     <t>stock géré par la maintenance, remplacées au fur et à mesure</t>
+  </si>
+  <si>
+    <t>sous contrat pour remplacement des piles</t>
+  </si>
+  <si>
+    <t>Dyler</t>
+  </si>
+  <si>
+    <t>en suspens</t>
+  </si>
+  <si>
+    <t>lors des travaux de rénovation</t>
+  </si>
+  <si>
+    <t>Wallon</t>
+  </si>
+  <si>
+    <t>équipement de nouveau reparti pour analyse chez le fournisseur
+réparé mais à nouveau grillé</t>
+  </si>
+  <si>
+    <t>²</t>
+  </si>
+  <si>
+    <t>Diffuseurs d'odeur</t>
+  </si>
+  <si>
+    <t>Resort</t>
+  </si>
+  <si>
+    <t>emo liquids</t>
+  </si>
+  <si>
+    <t>aménagement sortie de secours côté Meuse</t>
+  </si>
+  <si>
+    <t>Barco 04-223 56 54 Dune</t>
+  </si>
+  <si>
+    <t>Caméras reçues 27/05 - socles peints 28/05 - installation au retour de congé de Frank</t>
+  </si>
+  <si>
+    <t>Nettoyage + démolitions +/- 15/08 - début travaux septembre</t>
+  </si>
+  <si>
+    <t>Devis demandé chez ULTRASONS - rappel le 10/06
+prestataire à relancer - prototype semaine 33</t>
+  </si>
+  <si>
+    <t>Visite pour second devis semaine 33</t>
+  </si>
+  <si>
+    <t>1 des 2 à été remplacé, l'autre à un problème de communication - fournisseur cherche une solution - rappel fait le 04/08</t>
+  </si>
+  <si>
+    <t>LINERGY</t>
+  </si>
+  <si>
+    <t>commandé chez SKIDATA mais responsable ne travaille plus là… - rappel le 29/07</t>
+  </si>
+  <si>
+    <t>SKIDATA</t>
+  </si>
+  <si>
+    <t>Demandes de prix faites attente offres</t>
+  </si>
+  <si>
+    <t>Rappel BEGELEC le 18/05 - attente des plans de BALTEAU - vient le 14/08</t>
+  </si>
+  <si>
+    <t>nouveau test du 10/08 au 17/08</t>
+  </si>
+  <si>
+    <t>Offre à recevoir rappel fait le 29/05
+demande envoyée à un autre prestataire - Assa Abloy ne fait plus ces portes - Demande faite chez un 3ème</t>
+  </si>
+  <si>
+    <t>RAL envoyé - prévu mi-aout</t>
+  </si>
+  <si>
+    <t>test à faire - ICT doit configurer téléphones</t>
+  </si>
+  <si>
+    <t>prestataire passé, ça vient d'en bas - test avec ventilation prévu - dosage augmenté partout dans casino</t>
+  </si>
+  <si>
+    <t>Arrêté car hôtel full - reprend le 15/06 - reste 17 chambres le 07/08</t>
+  </si>
+  <si>
+    <t>Sterfput à créer et carrelage à acheter - date carrotage à recevoir du sous-traitant</t>
+  </si>
+  <si>
+    <t>optimiser odeurs casino - dosage augmenté</t>
+  </si>
+  <si>
+    <t>2 demandes de prix demandées</t>
+  </si>
+  <si>
+    <t>Fin betting</t>
+  </si>
+  <si>
+    <t>Bornes enlevées le 18/08 - JM et Greg doivent dire ce qu'ils veulent mettre dans la zone</t>
+  </si>
+  <si>
+    <t>procédure électricité</t>
+  </si>
+  <si>
+    <t>en attente de Jean-Louis</t>
+  </si>
+  <si>
+    <t>Betting</t>
+  </si>
+  <si>
+    <t>offre de prix reçue
+décision à prendre - voir Karim, Jérôme</t>
+  </si>
+  <si>
+    <t>offre de Stéphane DUBOIS envoyée à JM - attente JM</t>
+  </si>
+  <si>
+    <t>Marchandise arrivée au dépôt</t>
+  </si>
+  <si>
+    <t>Visite le 11/05 - devis en attente - dernier rappel le 22/05 - rappel par email + téléphone 05/06 - réception trespa pour réparation semaine 33 - porte prix à faire diminuer</t>
+  </si>
+  <si>
+    <t>Offre à corriger et compléter - relevé à faire par Jean-Louis</t>
+  </si>
+  <si>
+    <t>évacuation régulière en fonction de l'encombrement
++ faire appel à un container pour palettes</t>
+  </si>
+  <si>
+    <t>conteneur le 12/08
+à voir si quelqu'un peut venir les chercher</t>
   </si>
   <si>
     <t>normalement résolu par SCREEN SERVICES
 récurrence des problèmes à analyser
-lié aux encadrements TV</t>
-  </si>
-  <si>
-    <t>sous contrat pour remplacement des piles</t>
-  </si>
-  <si>
-    <t>Dyler</t>
-  </si>
-  <si>
-    <t>devis à valider</t>
-  </si>
-  <si>
-    <t>en suspens</t>
-  </si>
-  <si>
-    <t>lors des travaux de rénovation</t>
-  </si>
-  <si>
-    <t>Wallon</t>
-  </si>
-  <si>
-    <t>rapport reçu, rapport positif, attente début travaux
-prestataire n'a pas eu le temps</t>
-  </si>
-  <si>
-    <t>Devis demandé chez ULTRASONS - rappel le 10/06
-prestataire à relancer</t>
-  </si>
-  <si>
-    <t>équipement de nouveau reparti pour analyse chez le fournisseur
-réparé mais à nouveau grillé</t>
-  </si>
-  <si>
-    <t>prestataire passé, ça vient d'en bas - test avec ventilation prévu</t>
-  </si>
-  <si>
-    <t>offre de prix reçue
-décision à prendre</t>
-  </si>
-  <si>
-    <t>Offre à recevoir rappel fait le 29/05
-demande envoyée à un autre prestataire</t>
-  </si>
-  <si>
-    <t>²</t>
-  </si>
-  <si>
-    <t>Diffuseurs d'odeur</t>
-  </si>
-  <si>
-    <t>Resort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">optimiser odeurs casino </t>
-  </si>
-  <si>
-    <t>emo liquids</t>
-  </si>
-  <si>
-    <t>aménagement sortie de secours côté Meuse</t>
-  </si>
-  <si>
-    <t>Barco 04-223 56 54 Dune</t>
+lié aux encadrements TV
+1 en réserve</t>
+  </si>
+  <si>
+    <t>RENO ENERGIE prépare le dossier pour les pompiers - En attente du contrat pour la partie ENGIE mais déjà lancé
+2 commandes - rapide chez Engie, normale au sous-sol chez RENO - contrat à valider par le légal</t>
+  </si>
+  <si>
+    <t>Fin sol cuisine traiteur - Casino Club</t>
+  </si>
+  <si>
+    <t>Accès au GP dans cuisine LCDR</t>
+  </si>
+  <si>
+    <t>LCDR</t>
+  </si>
+  <si>
+    <t>Jérôme Farino - contact société</t>
+  </si>
+  <si>
+    <t>recherche d'un autre prestataire</t>
+  </si>
+  <si>
+    <t>Fait le 12/05 - procédure - produit 1x par semaine, sauf Casino Club (Maintenance tou les 4/5 mois)</t>
+  </si>
+  <si>
+    <t>Cuisine Yacht Club</t>
+  </si>
+  <si>
+    <t>Yacht Club</t>
+  </si>
+  <si>
+    <t>à mettre dans les capex
+four, électricité, hotte…</t>
+  </si>
+  <si>
+    <t>prise triphasée entrée hôtel</t>
+  </si>
+  <si>
+    <t>Hôtel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -830,6 +876,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos"/>
@@ -871,7 +924,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -903,6 +956,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -924,7 +992,7 @@
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -971,10 +1039,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}" name="Table2" displayName="Table2" ref="A1:M97" totalsRowShown="0" dataDxfId="13">
-  <autoFilter ref="A1:M97" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M96">
-    <sortCondition ref="C1:C96"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}" name="Table2" displayName="Table2" ref="A1:M100" totalsRowShown="0" dataDxfId="13">
+  <autoFilter ref="A1:M100" xr:uid="{0ADF688A-8753-492E-AE81-51C2ACD7EDE1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M98">
+    <sortCondition ref="C1:C98"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{4F006A25-C195-4CE0-BFA1-A12D1BA0DCFF}" name="Catégorie" dataDxfId="12"/>
@@ -1317,21 +1385,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M97"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M100"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="44.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.69921875" customWidth="1"/>
     <col min="4" max="4" width="10.5" customWidth="1"/>
-    <col min="5" max="5" width="15.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="51.25" customWidth="1"/>
-    <col min="9" max="13" width="35.75" customWidth="1"/>
+    <col min="5" max="5" width="15.69921875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.69921875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="10.69921875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="51.19921875" customWidth="1"/>
+    <col min="9" max="13" width="35.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1342,10 +1410,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -1372,12 +1440,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C2" s="4">
         <v>46185</v>
@@ -1387,80 +1455,80 @@
         <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>211</v>
+        <v>20</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>196</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3" s="4">
         <v>46188</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="H3" s="7"/>
       <c r="I3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="C4" s="4">
         <v>46188</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="H4" s="7"/>
       <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
@@ -1477,12 +1545,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="4">
         <v>46188</v>
@@ -1495,10 +1563,10 @@
         <v>14</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>172</v>
+        <v>20</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -1506,28 +1574,28 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="4">
         <v>46199</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>165</v>
+        <v>20</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>156</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -1535,12 +1603,12 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" s="4">
         <v>46199</v>
@@ -1550,84 +1618,84 @@
         <v>13</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>231</v>
+        <v>20</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="4">
         <v>46199</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>158</v>
+        <v>20</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" s="4">
         <v>46199</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="H9" s="7"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" s="4">
         <v>46199</v>
@@ -1637,40 +1705,40 @@
         <v>13</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="H10" s="7"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="4">
         <v>46199</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>169</v>
+        <v>20</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>16</v>
@@ -1679,7 +1747,7 @@
         <v>16</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>16</v>
@@ -1688,12 +1756,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4">
         <v>46199</v>
@@ -1704,9 +1772,9 @@
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -1725,12 +1793,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="4">
         <v>46199</v>
@@ -1741,14 +1809,14 @@
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="J13" s="3" t="s">
         <v>16</v>
       </c>
@@ -1762,12 +1830,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C14" s="4">
         <v>46199</v>
@@ -1777,36 +1845,36 @@
         <v>13</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>201</v>
+        <v>20</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>187</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="C15" s="4">
         <v>46199</v>
@@ -1819,10 +1887,10 @@
         <v>14</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>171</v>
+        <v>20</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>162</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>16</v>
@@ -1840,12 +1908,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C16" s="4">
         <v>46199</v>
@@ -1858,9 +1926,9 @@
         <v>14</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -1879,28 +1947,28 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C17" s="4">
         <v>46199</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="6" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>177</v>
+        <v>20</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -1908,12 +1976,12 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" s="4">
         <v>46199</v>
@@ -1923,13 +1991,13 @@
         <v>13</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>180</v>
+        <v>20</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>16</v>
@@ -1947,82 +2015,82 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C19" s="4">
         <v>46199</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="6" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="H19" s="7"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="4">
         <v>46199</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="H20" s="7"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C21" s="4">
         <v>46201</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>164</v>
+        <v>20</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>155</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -2030,59 +2098,59 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C22" s="4">
         <v>46218</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>208</v>
+        <v>20</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>193</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C23" s="4">
         <v>46218</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="6" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>217</v>
+        <v>20</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>198</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -2090,31 +2158,31 @@
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="4">
         <v>46218</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>16</v>
@@ -2123,34 +2191,34 @@
         <v>16</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="C25" s="4">
         <v>46233</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="6" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>175</v>
+        <v>20</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -2158,90 +2226,88 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>80</v>
+        <v>224</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>223</v>
       </c>
       <c r="C26" s="4">
-        <v>46233</v>
-      </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="6" t="s">
-        <v>136</v>
-      </c>
+        <v>46234</v>
+      </c>
+      <c r="D26" s="5">
+        <v>46234</v>
+      </c>
+      <c r="E26" s="6"/>
       <c r="F26" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I26" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>225</v>
+      </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>23</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>101</v>
       </c>
       <c r="C27" s="4">
-        <v>46234</v>
-      </c>
-      <c r="D27" s="5">
-        <v>46387</v>
-      </c>
+        <v>46235</v>
+      </c>
+      <c r="D27" s="3"/>
       <c r="E27" s="6" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>226</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C28" s="4">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="6" t="s">
-        <v>187</v>
+        <v>13</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -2249,86 +2315,94 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>48</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>72</v>
       </c>
       <c r="C29" s="4">
-        <v>46234</v>
-      </c>
-      <c r="D29" s="3"/>
+        <v>46248</v>
+      </c>
+      <c r="D29" s="5">
+        <v>46357</v>
+      </c>
       <c r="E29" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="I29" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="C30" s="4">
-        <v>46234</v>
-      </c>
-      <c r="D30" s="3"/>
+        <v>46249</v>
+      </c>
+      <c r="D30" s="5">
+        <v>46387</v>
+      </c>
       <c r="E30" s="6" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="I30" s="3"/>
+        <v>229</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C31" s="4">
-        <v>46234</v>
+        <v>46249</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="6" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>181</v>
+        <v>40</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>230</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -2336,28 +2410,28 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="C32" s="4">
-        <v>46234</v>
+        <v>46249</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="6" t="s">
-        <v>176</v>
+        <v>53</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>182</v>
+        <v>133</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -2365,15 +2439,15 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C33" s="4">
-        <v>46234</v>
+        <v>46249</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="6" t="s">
@@ -2383,39 +2457,41 @@
         <v>14</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I33" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>233</v>
+      </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C34" s="4">
-        <v>46234</v>
+        <v>46249</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>213</v>
+        <v>40</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>253</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
@@ -2423,179 +2499,187 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C35" s="4">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="6" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>214</v>
+        <v>28</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>234</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C36" s="4">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="6" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>254</v>
+      </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>107</v>
       </c>
       <c r="C37" s="4">
-        <v>46235</v>
-      </c>
-      <c r="D37" s="5"/>
+        <v>46249</v>
+      </c>
+      <c r="D37" s="3"/>
       <c r="E37" s="6" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I37" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>157</v>
+      </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C38" s="4">
-        <v>46235</v>
-      </c>
-      <c r="D38" s="5">
-        <v>46357</v>
-      </c>
+        <v>46249</v>
+      </c>
+      <c r="D38" s="5"/>
       <c r="E38" s="6" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>220</v>
+        <v>133</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>256</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>91</v>
+        <v>127</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="C39" s="4">
-        <v>46235</v>
-      </c>
-      <c r="D39" s="5"/>
+        <v>46249</v>
+      </c>
+      <c r="D39" s="3"/>
       <c r="E39" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="C40" s="4">
-        <v>46235</v>
-      </c>
-      <c r="D40" s="5"/>
+        <v>46249</v>
+      </c>
+      <c r="D40" s="3"/>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>232</v>
+        <v>28</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
@@ -2603,28 +2687,28 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="C41" s="4">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="6" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
@@ -2632,191 +2716,189 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>134</v>
+        <v>11</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="C42" s="4">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>32</v>
+        <v>23</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>106</v>
       </c>
       <c r="C43" s="4">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="6" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>163</v>
+        <v>40</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="I43" s="3"/>
-      <c r="J43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C44" s="4">
-        <v>46235</v>
-      </c>
-      <c r="D44" s="3"/>
+        <v>46249</v>
+      </c>
+      <c r="D44" s="5"/>
       <c r="E44" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>135</v>
+      </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="C45" s="4">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="6" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I45" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>12</v>
+        <v>48</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>212</v>
       </c>
       <c r="C46" s="4">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="6" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="C47" s="4">
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>167</v>
+        <v>15</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
@@ -2824,121 +2906,113 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>107</v>
+        <v>263</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>262</v>
       </c>
       <c r="C48" s="4">
         <v>46249</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="6" t="s">
-        <v>13</v>
+        <v>136</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H48" s="7" t="s">
-        <v>250</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="H48" s="7"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C49" s="4">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>139</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="C50" s="4">
-        <v>46249</v>
+        <v>46264</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="6" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>153</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>234</v>
+        <v>131</v>
       </c>
       <c r="C51" s="4">
-        <v>46249</v>
+        <v>46264</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>156</v>
+        <v>49</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
@@ -2946,28 +3020,28 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="C52" s="4">
-        <v>46249</v>
+        <v>46264</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="6" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>163</v>
+        <v>49</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
@@ -2975,28 +3049,28 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C53" s="4">
         <v>46264</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>210</v>
+        <v>28</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>195</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
@@ -3004,28 +3078,26 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C54" s="4">
+        <v>46264</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B54" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C54" s="4">
-        <v>46265</v>
-      </c>
-      <c r="D54" s="3"/>
-      <c r="E54" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>212</v>
+      <c r="H54" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
@@ -3033,43 +3105,41 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="1:13" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C55" s="4">
         <v>46265</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="6" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>227</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>225</v>
+        <v>23</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="C56" s="4">
         <v>46265</v>
@@ -3081,79 +3151,67 @@
       <c r="F56" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G56" s="6"/>
-      <c r="H56" s="3" t="s">
-        <v>248</v>
+      <c r="G56" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>221</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>44</v>
+        <v>205</v>
       </c>
       <c r="C57" s="4">
-        <v>46266</v>
-      </c>
-      <c r="D57" s="5"/>
+        <v>46265</v>
+      </c>
+      <c r="D57" s="3"/>
       <c r="E57" s="6" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>215</v>
+      <c r="G57" s="6"/>
+      <c r="H57" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>69</v>
+        <v>52</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="C58" s="4">
-        <v>46266</v>
-      </c>
-      <c r="D58" s="5"/>
-      <c r="E58" s="6" t="s">
-        <v>136</v>
-      </c>
+        <v>46265</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="6"/>
       <c r="F58" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>216</v>
+      <c r="G58" s="6"/>
+      <c r="H58" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
@@ -3161,156 +3219,156 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>127</v>
+        <v>48</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="C59" s="4">
         <v>46266</v>
       </c>
-      <c r="D59" s="3"/>
-      <c r="E59" s="8" t="s">
-        <v>13</v>
+      <c r="D59" s="5"/>
+      <c r="E59" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>229</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>71</v>
+        <v>124</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="C60" s="4">
         <v>46266</v>
       </c>
-      <c r="D60" s="3"/>
+      <c r="D60" s="5"/>
       <c r="E60" s="6" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>28</v>
+        <v>124</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="C61" s="4">
         <v>46266</v>
       </c>
-      <c r="D61" s="3"/>
+      <c r="D61" s="5"/>
       <c r="E61" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M61" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="1:13" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="C62" s="4">
         <v>46266</v>
       </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="6" t="s">
+      <c r="D62" s="3"/>
+      <c r="E62" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="I62" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C63" s="4">
         <v>46266</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="6" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>154</v>
+        <v>28</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
@@ -3318,57 +3376,67 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>76</v>
+        <v>23</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="C64" s="4">
         <v>46266</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="6" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>77</v>
+        <v>261</v>
       </c>
       <c r="C65" s="4">
         <v>46266</v>
       </c>
-      <c r="D65" s="3"/>
+      <c r="D65" s="5"/>
       <c r="E65" s="6" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>154</v>
+        <v>133</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
@@ -3376,28 +3444,28 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C66" s="4">
         <v>46266</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>154</v>
+        <v>49</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>146</v>
       </c>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
@@ -3405,28 +3473,28 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="C67" s="4">
         <v>46266</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="6" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>233</v>
+        <v>49</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>146</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
@@ -3434,28 +3502,28 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="C68" s="4">
         <v>46266</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="6" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>163</v>
+        <v>49</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>146</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
@@ -3463,150 +3531,138 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>36</v>
+        <v>48</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="C69" s="4">
         <v>46266</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="6" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C70" s="4">
         <v>46266</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="6" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>170</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="I70" s="3"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>202</v>
+        <v>127</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="C71" s="4">
         <v>46266</v>
       </c>
-      <c r="D71" s="4">
-        <v>46388</v>
-      </c>
+      <c r="D71" s="3"/>
       <c r="E71" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F71" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M71" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+      <c r="K71" s="3"/>
+      <c r="L71" s="3"/>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>94</v>
+        <v>127</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="C72" s="4">
         <v>46266</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="6" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C73" s="4">
         <v>46266</v>
@@ -3616,55 +3672,69 @@
         <v>13</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="I73" s="3"/>
+        <v>28</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>105</v>
+        <v>124</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>188</v>
       </c>
       <c r="C74" s="4">
         <v>46266</v>
       </c>
-      <c r="D74" s="3"/>
+      <c r="D74" s="4">
+        <v>46388</v>
+      </c>
       <c r="E74" s="6" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C75" s="4">
         <v>46266</v>
@@ -3674,24 +3744,26 @@
         <v>13</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H75" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>264</v>
+      </c>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C76" s="4">
         <v>46266</v>
@@ -3701,13 +3773,13 @@
         <v>13</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>190</v>
+        <v>28</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
@@ -3715,12 +3787,12 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C77" s="4">
         <v>46266</v>
@@ -3730,13 +3802,13 @@
         <v>13</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>191</v>
+        <v>40</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
@@ -3744,12 +3816,12 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C78" s="4">
         <v>46266</v>
@@ -3762,10 +3834,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>192</v>
+        <v>40</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>265</v>
       </c>
       <c r="I78" s="3"/>
       <c r="J78" s="3"/>
@@ -3773,12 +3845,12 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="C79" s="4">
         <v>46266</v>
@@ -3788,13 +3860,13 @@
         <v>13</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>193</v>
+        <v>28</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>176</v>
       </c>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
@@ -3802,587 +3874,680 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>51</v>
+        <v>56</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="C80" s="4">
-        <v>46295</v>
+        <v>46266</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="6" t="s">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M80" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B81" s="10" t="s">
         <v>56</v>
       </c>
+      <c r="B81" s="9" t="s">
+        <v>83</v>
+      </c>
       <c r="C81" s="4">
-        <v>46296</v>
+        <v>46266</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="6" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>195</v>
+        <v>56</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>113</v>
       </c>
       <c r="C82" s="4">
-        <v>46388</v>
+        <v>46266</v>
       </c>
       <c r="D82" s="3"/>
-      <c r="E82" s="6"/>
+      <c r="E82" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="F82" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>53</v>
+        <v>251</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>55</v>
+        <v>247</v>
       </c>
       <c r="C83" s="4">
-        <v>46388</v>
+        <v>46269</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="6" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="31.5" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="G83" s="6"/>
+      <c r="H83" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C84" s="4">
-        <v>46478</v>
+        <v>46295</v>
       </c>
       <c r="D84" s="3"/>
       <c r="E84" s="6" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H84" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H84" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C85" s="4">
+        <v>46296</v>
+      </c>
+      <c r="D85" s="3"/>
+      <c r="E85" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="C86" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D86" s="3"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K86" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I84" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K84" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="L84" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M84" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B85" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C85" s="4">
-        <v>46508</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G85" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3"/>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B86" s="9" t="s">
+      <c r="L86" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C87" s="4">
+        <v>46388</v>
+      </c>
+      <c r="D87" s="3"/>
+      <c r="E87" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C86" s="4"/>
-      <c r="D86" s="5">
-        <v>46357</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B87" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C87" s="4"/>
-      <c r="D87" s="5">
-        <v>46387</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I87" s="3"/>
-      <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="B88" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C88" s="4"/>
+        <v>33</v>
+      </c>
+      <c r="C88" s="4">
+        <v>46478</v>
+      </c>
       <c r="D88" s="3"/>
       <c r="E88" s="6" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>237</v>
+        <v>183</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>266</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="J88" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K88" s="3" t="s">
-        <v>43</v>
+      <c r="K88" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="M88" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B89" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C89" s="4"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="6"/>
+        <v>122</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C89" s="4">
+        <v>46508</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="F89" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H89" s="7"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+      <c r="K89" s="3"/>
+      <c r="L89" s="3"/>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B90" s="10" t="s">
         <v>48</v>
       </c>
+      <c r="B90" s="9" t="s">
+        <v>120</v>
+      </c>
       <c r="C90" s="4"/>
-      <c r="D90" s="3"/>
+      <c r="D90" s="5">
+        <v>46357</v>
+      </c>
       <c r="E90" s="6" t="s">
-        <v>240</v>
+        <v>139</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="3"/>
+      <c r="L90" s="3"/>
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B91" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C91" s="4"/>
-      <c r="D91" s="3"/>
+      <c r="D91" s="5">
+        <v>46387</v>
+      </c>
       <c r="E91" s="6" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="3"/>
+      <c r="L91" s="3"/>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>113</v>
+        <v>124</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>189</v>
       </c>
       <c r="C92" s="4"/>
       <c r="D92" s="3"/>
       <c r="E92" s="6" t="s">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M92" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>87</v>
+        <v>23</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>180</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="3"/>
-      <c r="E93" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="E93" s="6"/>
       <c r="F93" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="I93" s="3"/>
-      <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="3"/>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>67</v>
+        <v>45</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>47</v>
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="3"/>
       <c r="E94" s="6" t="s">
-        <v>54</v>
+        <v>217</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3"/>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="H94" s="7"/>
+      <c r="I94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>109</v>
+        <v>45</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>46</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="3"/>
       <c r="E95" s="6" t="s">
-        <v>54</v>
+        <v>217</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="H95" s="7"/>
+      <c r="I95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C96" s="4"/>
-      <c r="D96" s="5">
-        <v>46234</v>
-      </c>
-      <c r="E96" s="6"/>
+        <v>128</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C96" s="4">
+        <v>46310</v>
+      </c>
+      <c r="D96" s="3"/>
+      <c r="E96" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="F96" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>255</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="I96" s="3"/>
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>256</v>
+        <v>128</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C97" s="4">
-        <v>46295</v>
+        <v>46310</v>
       </c>
       <c r="D97" s="3"/>
-      <c r="E97" s="6"/>
+      <c r="E97" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="F97" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H97" s="3"/>
+        <v>218</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>219</v>
+      </c>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C98" s="4">
+        <v>46310</v>
+      </c>
+      <c r="D98" s="3"/>
+      <c r="E98" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C99" s="4">
+        <v>46280</v>
+      </c>
+      <c r="D99" s="3"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="3"/>
+      <c r="L99" s="3"/>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C100" s="4">
+        <v>46249</v>
+      </c>
+      <c r="D100" s="3"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="7"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="3"/>
+      <c r="M100" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
